--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_99_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_99_R10.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5935</v>
+        <v>8.3942</v>
       </c>
       <c r="E2" t="n">
-        <v>8.856999999999999</v>
+        <v>6.9265</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7365</v>
+        <v>1.4676</v>
       </c>
       <c r="G2" t="n">
         <v>4.9424</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2594</v>
+        <v>2.0601</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3422</v>
+        <v>1.4117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9173</v>
+        <v>0.6484</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.629</v>
+        <v>4.5825</v>
       </c>
       <c r="E3" t="n">
-        <v>1.724</v>
+        <v>1.7551</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9049</v>
+        <v>2.8274</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4588</v>
+        <v>4.8925</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3843</v>
+        <v>2.3061</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0745</v>
+        <v>2.5864</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5807</v>
+        <v>4.6998</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1883</v>
+        <v>1.9529</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3923</v>
+        <v>2.7469</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1219</v>
+        <v>0.1927</v>
       </c>
       <c r="N3" t="n">
-        <v>0.196</v>
+        <v>0.3532</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3178</v>
+        <v>-0.1605</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9278</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>-4.871</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0979</v>
+        <v>1.2079</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6948</v>
+        <v>0.4288</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4031</v>
+        <v>0.7791</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.4975</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.4975</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5306</v>
+        <v>3.8525</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7368</v>
+        <v>1.2836</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7938</v>
+        <v>2.5689</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8925</v>
+        <v>2.4588</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3061</v>
+        <v>0.3843</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5864</v>
+        <v>2.0745</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6998</v>
+        <v>2.5807</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9529</v>
+        <v>0.1883</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7469</v>
+        <v>2.3923</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1927</v>
+        <v>-0.1219</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3532</v>
+        <v>0.196</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1605</v>
+        <v>-0.3178</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.0154</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.871</v>
+        <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>0.156</v>
+        <v>2.3215</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5895</v>
+        <v>1.2544</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7455000000000001</v>
+        <v>1.0671</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4975</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4975</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0163</v>
+        <v>1.1507</v>
       </c>
       <c r="E5" t="n">
         <v>-0.0621</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0784</v>
+        <v>1.2129</v>
       </c>
       <c r="G5" t="n">
         <v>0.3802</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0597</v>
+        <v>0.0747</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6437</v>
+        <v>0.6272</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0973</v>
+        <v>1.2152</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4536</v>
+        <v>-0.588</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4185</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5614</v>
+        <v>-0.5779</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5895</v>
+        <v>-0.4716</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0281</v>
+        <v>-0.1063</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7635</v>
+        <v>-0.0751</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6816</v>
+        <v>1.3028</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4451</v>
+        <v>-1.3779</v>
       </c>
       <c r="G7" t="n">
         <v>0.6322</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9498</v>
+        <v>-0.2614</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7389</v>
+        <v>-0.1177</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6778999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2348</v>
+        <v>-1.6211</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3897</v>
+        <v>-0.8433</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8451</v>
+        <v>-0.7779</v>
       </c>
       <c r="G8" t="n">
         <v>-2.759</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7257</v>
+        <v>-0.112</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5895</v>
+        <v>-0.0431</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1362</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7413</v>
+        <v>-2.1441</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6579</v>
+        <v>-1.9934</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0834</v>
+        <v>-0.1506</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7479</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4419</v>
+        <v>0.1553</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5895</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1476</v>
+        <v>0.0804</v>
       </c>
       <c r="V9" t="n">
         <v>0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1776</v>
+        <v>-2.6552</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.8395</v>
+        <v>-4.8212</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6619</v>
+        <v>2.166</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1561</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7174</v>
+        <v>0.805</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7389</v>
+        <v>0.2794</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0215</v>
+        <v>0.5256</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6171</v>
+        <v>-5.368</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0529</v>
+        <v>-3.8038</v>
       </c>
       <c r="F11" t="n">
         <v>-1.5642</v>
@@ -1312,10 +1312,10 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9594</v>
+        <v>0.2084</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0578</v>
+        <v>0.3068</v>
       </c>
       <c r="U11" t="n">
         <v>-0.0984</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5776</v>
+        <v>-5.6956</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.749</v>
+        <v>-4.8669</v>
       </c>
       <c r="F12" t="n">
         <v>-0.8286</v>
@@ -1390,10 +1390,10 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.861</v>
+        <v>0.7431</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2715</v>
+        <v>0.1535</v>
       </c>
       <c r="U12" t="n">
         <v>0.5895</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3012000000000006</v>
+        <v>1.047999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.654400000000002</v>
+        <v>-3.9075</v>
       </c>
       <c r="F13" t="n">
-        <v>4.955500000000001</v>
+        <v>4.9556</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5044</v>
@@ -1441,7 +1441,7 @@
         <v>-2.8779</v>
       </c>
       <c r="J13" t="n">
-        <v>6.631500000000001</v>
+        <v>6.631499999999997</v>
       </c>
       <c r="K13" t="n">
         <v>1.864300000000001</v>
@@ -1468,13 +1468,13 @@
         <v>16.2368</v>
       </c>
       <c r="S13" t="n">
-        <v>5.877800000000001</v>
+        <v>6.624699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3811</v>
+        <v>3.1277</v>
       </c>
       <c r="U13" t="n">
-        <v>3.496700000000001</v>
+        <v>3.4968</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0723</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2767</v>
+        <v>5.519</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3805</v>
+        <v>4.7343</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8962</v>
+        <v>0.7846</v>
       </c>
       <c r="G14" t="n">
         <v>5.0316</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1466</v>
+        <v>-0.9043</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0263</v>
+        <v>-0.1379</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4737</v>
+        <v>1.497</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3463</v>
+        <v>0.9463</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1275</v>
+        <v>0.5506</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3372</v>
+        <v>3.0022</v>
       </c>
       <c r="H15" t="n">
-        <v>0.168</v>
+        <v>-0.2232</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5052</v>
+        <v>3.2254</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6317</v>
+        <v>3.3954</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5581</v>
+        <v>-0.1478</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0736</v>
+        <v>3.5432</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9688</v>
+        <v>-0.3933</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.39</v>
+        <v>-0.0755</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5788</v>
+        <v>-0.3178</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.329</v>
+        <v>-0.0413</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5895</v>
+        <v>-0.1296</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9186</v>
+        <v>0.0883</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0366</v>
+        <v>1.2892</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7104</v>
+        <v>0.4642</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3262</v>
+        <v>0.825</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0022</v>
+        <v>-0.3372</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2232</v>
+        <v>0.168</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2254</v>
+        <v>-0.5052</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3954</v>
+        <v>0.6317</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1478</v>
+        <v>0.5581</v>
       </c>
       <c r="L16" t="n">
-        <v>3.5432</v>
+        <v>0.0736</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3933</v>
+        <v>-0.9688</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0755</v>
+        <v>-0.39</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3178</v>
+        <v>-0.5788</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5017</v>
+        <v>0.1445</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3655</v>
+        <v>-0.4716</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1362</v>
+        <v>0.6161</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9013</v>
+        <v>0.6711</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2136</v>
+        <v>-0.5675</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1149</v>
+        <v>1.2386</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2051</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5909</v>
+        <v>0.3607</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4208</v>
+        <v>0.067</v>
       </c>
       <c r="U17" t="n">
-        <v>0.17</v>
+        <v>0.2937</v>
       </c>
       <c r="V17" t="n">
         <v>0.2836</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7976</v>
+        <v>0.3488</v>
       </c>
       <c r="E18" t="n">
-        <v>0.466</v>
+        <v>-0.408</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3316</v>
+        <v>0.7569</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1976</v>
+        <v>0.3774</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0266</v>
+        <v>0.461</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2242</v>
+        <v>-0.0837</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0983</v>
+        <v>-0.3766</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.3361</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0171</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9006999999999999</v>
+        <v>0.754</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1078</v>
+        <v>0.1249</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7929</v>
+        <v>0.6291</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9221</v>
+        <v>-0.2605</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5454</v>
+        <v>-0.0314</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6234</v>
+        <v>-0.2291</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0196</v>
+        <v>0.0934</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0293</v>
+        <v>-0.5282</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.049</v>
+        <v>0.6216</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1754</v>
+        <v>1.4449</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1921</v>
+        <v>1.0299</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0167</v>
+        <v>0.415</v>
       </c>
       <c r="J19" t="n">
-        <v>0.104</v>
+        <v>1.9061</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0672</v>
+        <v>1.17</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0.7361</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.4612</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1249</v>
+        <v>-0.1401</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0535</v>
+        <v>-0.3211</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.427</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0747</v>
+        <v>-0.7231</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3523</v>
+        <v>0.0674</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0272</v>
+        <v>0.0476</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.526</v>
+        <v>0.0293</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4988</v>
+        <v>0.0183</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3774</v>
+        <v>0.1754</v>
       </c>
       <c r="H20" t="n">
-        <v>0.461</v>
+        <v>0.1921</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0837</v>
+        <v>-0.0167</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3766</v>
+        <v>0.104</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3361</v>
+        <v>0.0672</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.754</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>0.1249</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6291</v>
+        <v>-0.0535</v>
       </c>
       <c r="P20" t="n">
         <v>0.232</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6365</v>
+        <v>-0.3598</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4872</v>
+        <v>-0.2851</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3233</v>
+        <v>-0.1746</v>
       </c>
       <c r="E21" t="n">
-        <v>-1</v>
+        <v>-0.8315</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6767</v>
+        <v>0.6569</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4449</v>
+        <v>0.1976</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0299</v>
+        <v>-0.0266</v>
       </c>
       <c r="I21" t="n">
-        <v>0.415</v>
+        <v>0.2242</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9061</v>
+        <v>1.0983</v>
       </c>
       <c r="K21" t="n">
-        <v>1.17</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7361</v>
+        <v>1.0171</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4612</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1401</v>
+        <v>-0.1078</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3211</v>
+        <v>-0.7929</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7834</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0723</v>
+        <v>-0.0501</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1949</v>
+        <v>0.248</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1226</v>
+        <v>-0.2981</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.341</v>
+        <v>-0.3686</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6811</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0221</v>
+        <v>0.3527</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1069</v>
+        <v>-0.9067</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1202</v>
+        <v>0.1573</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0133</v>
+        <v>-1.064</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5001</v>
+        <v>-0.0272</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3529</v>
+        <v>0.612</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1472</v>
+        <v>-0.6391</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3933</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2327</v>
+        <v>-0.4547</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1605</v>
+        <v>-0.4248</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3962</v>
+        <v>-1.3897</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4129</v>
+        <v>-0.7664</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8092</v>
+        <v>-0.6234</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2836</v>
+        <v>0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1941</v>
+        <v>-0.4539</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9614</v>
+        <v>0.2093</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2328</v>
+        <v>-0.6632</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5942</v>
+        <v>0.1069</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1151</v>
+        <v>0.1202</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7093</v>
+        <v>-0.0133</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7236</v>
+        <v>0.5001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1176</v>
+        <v>0.3529</v>
       </c>
       <c r="L23" t="n">
-        <v>1.606</v>
+        <v>0.1472</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1294</v>
+        <v>-0.3933</v>
       </c>
       <c r="N23" t="n">
         <v>-0.2327</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8966</v>
+        <v>-0.1605</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3967</v>
+        <v>-0.5091</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3655</v>
+        <v>-0.0589</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0312</v>
+        <v>-0.4503</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2158</v>
+        <v>-0.7002</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0752</v>
+        <v>-0.7255</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1406</v>
+        <v>0.0253</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9067</v>
+        <v>0.5942</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1573</v>
+        <v>-0.1151</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.064</v>
+        <v>0.7093</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0272</v>
+        <v>1.7236</v>
       </c>
       <c r="K24" t="n">
-        <v>0.612</v>
+        <v>0.1176</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6391</v>
+        <v>1.606</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-1.1294</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4547</v>
+        <v>-0.2327</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4248</v>
+        <v>-0.8966</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3917</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2369</v>
+        <v>0.0973</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1202</v>
+        <v>-0.1296</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1167</v>
+        <v>0.2269</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.666</v>
+        <v>-6.4973</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.793</v>
+        <v>-7.5571</v>
       </c>
       <c r="F25" t="n">
-        <v>1.127</v>
+        <v>1.0598</v>
       </c>
       <c r="G25" t="n">
         <v>-4.9768</v>
@@ -2404,13 +2404,13 @@
         <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9058</v>
+        <v>-0.7371</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0097</v>
+        <v>-0.0769</v>
       </c>
       <c r="V25" t="n">
         <v>1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.301099999999999</v>
+        <v>1.2715</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9556</v>
+        <v>-4.9557</v>
       </c>
       <c r="F26" t="n">
-        <v>4.6544</v>
+        <v>6.227100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>4.5044</v>
@@ -2473,7 +2473,7 @@
         <v>-4.766999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0001999999999995339</v>
+        <v>0.0002000000000002</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.2367</v>
@@ -2482,13 +2482,13 @@
         <v>16.2367</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.8777</v>
+        <v>-4.305099999999999</v>
       </c>
       <c r="T26" t="n">
         <v>-3.497</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.381</v>
+        <v>-0.8083999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>1.0722</v>
